--- a/khurana_cv/data/pubs.xlsx
+++ b/khurana_cv/data/pubs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\havis\University of Oregon Dropbox\Havi Khurana\Personal\Coding projects\khurana_cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DC0212-644F-426F-A751-4A1CA25520C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5504B3DE-2BAA-46D2-9CEF-A0C020B34CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>type</t>
   </si>
@@ -157,12 +157,6 @@
     <t>May, 2024</t>
   </si>
   <si>
-    <t>presentation</t>
-  </si>
-  <si>
-    <t>Virtual</t>
-  </si>
-  <si>
     <t>December, 2023</t>
   </si>
   <si>
@@ -191,6 +185,81 @@
   </si>
   <si>
     <t>February, 2025</t>
+  </si>
+  <si>
+    <t>Khurana, H.</t>
+  </si>
+  <si>
+    <t>October, 2025</t>
+  </si>
+  <si>
+    <t>Society for Research on Educational Effectiveness</t>
+  </si>
+  <si>
+    <t>Illinois, Chicago</t>
+  </si>
+  <si>
+    <t>Grantmakers for Educations</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>iMentor College: Mapping Text-Prompt Response Rate and Pair Connection</t>
+  </si>
+  <si>
+    <t>Characterizing Variation in Special Education Revenues and Expenditures Using Oregon’s School Funding Formula</t>
+  </si>
+  <si>
+    <t>Leveraging Research for Philanthropic Strategy Setting: iMentor College: Mapping Text-Prompt Response Rate and Pair Connection</t>
+  </si>
+  <si>
+    <t>Kindergarten phonemic knowledge: A psychometric comparison of phonemic awareness and letter-sound correspondence task</t>
+  </si>
+  <si>
+    <t>Calgary, Canada</t>
+  </si>
+  <si>
+    <t>The Society for the Scientific Study of Reading</t>
+  </si>
+  <si>
+    <t>Biancarosa, G., Gallo,J., Lussier,C., Khurana, H., Kennedy, P.</t>
+  </si>
+  <si>
+    <t>July, 2025</t>
+  </si>
+  <si>
+    <t>Effect of Academic Criteria in English Learner Reclassification Policy</t>
+  </si>
+  <si>
+    <t>Umansky, I., Khurana, H.</t>
+  </si>
+  <si>
+    <t>Thompson, K., Khurana, H., Bovee, J.</t>
+  </si>
+  <si>
+    <t>Integerated English Language Development Program in Oregon</t>
+  </si>
+  <si>
+    <t>DIBELS® 8 Nonsense Word Fluency: Comparison of Administration Directions</t>
+  </si>
+  <si>
+    <t>Kennedy, P., Khurana, H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A Comparison of DIBELS 8th Edition Composite Score Percentile Ranks and Zones of Growth</t>
+  </si>
+  <si>
+    <t>Access to and Effect of Tutoring Programs in a Large Urban District</t>
+  </si>
+  <si>
+    <t>September, 2025</t>
+  </si>
+  <si>
+    <t>forthcoming</t>
+  </si>
+  <si>
+    <t>Executive Report and Internal Brief</t>
   </si>
 </sst>
 </file>
@@ -278,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -300,6 +369,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1460,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -1546,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="17.149999999999999" customHeight="1">
@@ -1554,53 +1625,54 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="6"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="15"/>
     </row>
     <row r="3" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>27</v>
+        <v>71</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="5"/>
+        <v>72</v>
+      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -1608,81 +1680,56 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
-      <c r="N3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="2"/>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
-      <c r="X3" s="1" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="4" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="15"/>
     </row>
     <row r="5" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1690,13 +1737,13 @@
       <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>44</v>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1704,74 +1751,63 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="2"/>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
-      <c r="X5" s="1" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="6" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
       <c r="N6" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P6" s="7" t="b">
+      <c r="P6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="8"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
       <c r="X6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="17.149999999999999" customHeight="1">
@@ -1779,386 +1815,572 @@
         <v>13</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="10" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" t="s">
+        <v>49</v>
       </c>
       <c r="O7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P7" s="7" t="b">
+      <c r="P7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="R7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="R7" s="7"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
       <c r="X7" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="11" t="s">
-        <v>38</v>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="O8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R8" s="7"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
+      <c r="P8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
       <c r="X8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="2"/>
+      <c r="Q9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" s="7"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
       <c r="U9" s="8"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
+      <c r="X9" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="8"/>
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="7"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
+      <c r="X10" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="8"/>
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3">
+        <v>6</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
     </row>
     <row r="12" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="3"/>
+      <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3">
+        <v>4</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" s="7"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="5"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
+      <c r="X12" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="13" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="K13" s="2"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="6"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="8"/>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
     </row>
     <row r="14" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="K14" s="2"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="N14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="3"/>
       <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="8"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
     </row>
     <row r="15" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="K15" s="2"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="N15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="6"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="8"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
     </row>
     <row r="16" spans="1:24" ht="17.149999999999999" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3">
+        <v>5</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+      <c r="K16" s="2"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="N16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="3"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="6"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="8"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
     </row>
-    <row r="17" spans="1:23" ht="17.149999999999999" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+    <row r="17" spans="1:24" ht="17.149999999999999" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="K17" s="2"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" s="3"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="3"/>
+      <c r="Q17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R17" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
-      <c r="U17" s="6"/>
+      <c r="U17" s="8"/>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
-    </row>
-    <row r="18" spans="1:23" ht="17.149999999999999" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="X17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="17.149999999999999" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="K18" s="2"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="2"/>
+      <c r="N18" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="3"/>
+      <c r="Q18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R18" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
-      <c r="U18" s="6"/>
+      <c r="U18" s="8"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
-    </row>
-    <row r="19" spans="1:23" ht="17.149999999999999" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="X18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="17.149999999999999" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+      <c r="K19" s="2"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="2"/>
+      <c r="N19" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" s="3"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="5"/>
+      <c r="Q19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="R19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2"/>
       <c r="T19" s="5"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
-    </row>
-    <row r="20" spans="1:23" ht="17.149999999999999" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="X19" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="17.149999999999999" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -2167,18 +2389,25 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
-      <c r="N20" s="2"/>
+      <c r="N20" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="2"/>
+      <c r="Q20" t="s">
+        <v>65</v>
+      </c>
       <c r="R20" s="3"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
-    </row>
-    <row r="21" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="X20" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="2"/>
@@ -2203,7 +2432,7 @@
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
     </row>
-    <row r="22" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="22" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
@@ -2228,7 +2457,7 @@
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
     </row>
-    <row r="23" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="23" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
@@ -2253,7 +2482,7 @@
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
     </row>
-    <row r="24" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="24" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
@@ -2278,7 +2507,7 @@
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
     </row>
-    <row r="25" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="25" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
@@ -2303,7 +2532,7 @@
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
     </row>
-    <row r="26" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="26" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
@@ -2328,7 +2557,7 @@
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
     </row>
-    <row r="27" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="27" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
@@ -2353,7 +2582,7 @@
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
     </row>
-    <row r="28" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="28" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
@@ -2378,7 +2607,7 @@
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
     </row>
-    <row r="29" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="29" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="2"/>
@@ -2403,7 +2632,7 @@
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
     </row>
-    <row r="30" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="30" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="2"/>
@@ -2428,7 +2657,7 @@
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
     </row>
-    <row r="31" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="31" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="2"/>
@@ -2453,7 +2682,7 @@
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
     </row>
-    <row r="32" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="32" spans="1:24" ht="17.149999999999999" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="2"/>
@@ -2528,7 +2757,7 @@
       <c r="V34" s="6"/>
       <c r="W34" s="6"/>
     </row>
-    <row r="35" spans="1:23" ht="18" customHeight="1">
+    <row r="35" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="2"/>
@@ -2553,7 +2782,7 @@
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
     </row>
-    <row r="36" spans="1:23" ht="18" customHeight="1">
+    <row r="36" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="2"/>
@@ -2607,7 +2836,7 @@
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
+      <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2616,13 +2845,13 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="2"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="5"/>
       <c r="T38" s="5"/>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
@@ -2632,7 +2861,7 @@
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -2641,13 +2870,13 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="2"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="5"/>
       <c r="T39" s="5"/>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
@@ -2657,7 +2886,7 @@
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2666,13 +2895,13 @@
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="2"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="5"/>
       <c r="T40" s="5"/>
       <c r="U40" s="6"/>
       <c r="V40" s="6"/>
@@ -2682,7 +2911,7 @@
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="3"/>
+      <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -2691,24 +2920,24 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="2"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="5"/>
       <c r="T41" s="5"/>
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
     </row>
-    <row r="42" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="42" spans="1:23" ht="18" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="9"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -2716,24 +2945,24 @@
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="2"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="5"/>
       <c r="T42" s="5"/>
       <c r="U42" s="6"/>
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
     </row>
-    <row r="43" spans="1:23" ht="17.149999999999999" customHeight="1">
+    <row r="43" spans="1:23" ht="18" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="9"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -2741,13 +2970,13 @@
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="2"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="5"/>
       <c r="T43" s="5"/>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
@@ -2757,7 +2986,7 @@
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2766,13 +2995,13 @@
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="2"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="5"/>
       <c r="T44" s="5"/>
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
@@ -2791,7 +3020,7 @@
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
-      <c r="M45" s="9"/>
+      <c r="M45" s="2"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
@@ -2816,7 +3045,7 @@
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
-      <c r="M46" s="9"/>
+      <c r="M46" s="2"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
@@ -2857,74 +3086,74 @@
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="8"/>
+      <c r="D48" s="3"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="6"/>
-      <c r="T48" s="6"/>
-      <c r="U48" s="8"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="6"/>
       <c r="V48" s="6"/>
       <c r="W48" s="6"/>
     </row>
     <row r="49" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="8"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="6"/>
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
     </row>
     <row r="50" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="8"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="6"/>
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
     </row>
@@ -2932,24 +3161,24 @@
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="3"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="8"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
     </row>
@@ -2957,82 +3186,82 @@
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="3"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="8"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="5"/>
       <c r="U52" s="6"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="8"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
     </row>
     <row r="53" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="7"/>
+      <c r="D53" s="3"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="8"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="5"/>
       <c r="U53" s="6"/>
-      <c r="V53" s="8"/>
+      <c r="V53" s="6"/>
       <c r="W53" s="6"/>
     </row>
     <row r="54" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="7"/>
+      <c r="D54" s="3"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="8"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="5"/>
       <c r="U54" s="6"/>
-      <c r="V54" s="2"/>
+      <c r="V54" s="6"/>
       <c r="W54" s="6"/>
     </row>
     <row r="55" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="7"/>
+      <c r="D55" s="8"/>
       <c r="E55" s="2"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
@@ -3042,22 +3271,22 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
       <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="7"/>
       <c r="S55" s="6"/>
-      <c r="T55" s="8"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="8"/>
-      <c r="W55" s="8"/>
+      <c r="T55" s="6"/>
+      <c r="U55" s="8"/>
+      <c r="V55" s="6"/>
+      <c r="W55" s="6"/>
     </row>
     <row r="56" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="7"/>
+      <c r="D56" s="8"/>
       <c r="E56" s="2"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
@@ -3067,22 +3296,22 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
       <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="7"/>
       <c r="S56" s="6"/>
-      <c r="T56" s="8"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="2"/>
+      <c r="T56" s="6"/>
+      <c r="U56" s="8"/>
+      <c r="V56" s="6"/>
       <c r="W56" s="6"/>
     </row>
     <row r="57" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="7"/>
+      <c r="D57" s="8"/>
       <c r="E57" s="2"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
@@ -3092,23 +3321,23 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
       <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="7"/>
       <c r="S57" s="6"/>
-      <c r="T57" s="8"/>
-      <c r="U57" s="6"/>
-      <c r="V57" s="2"/>
+      <c r="T57" s="6"/>
+      <c r="U57" s="8"/>
+      <c r="V57" s="6"/>
       <c r="W57" s="6"/>
     </row>
     <row r="58" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="2"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -3117,16 +3346,16 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
       <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="7"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="8"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
     </row>
     <row r="59" spans="1:23" ht="17.149999999999999" customHeight="1">
       <c r="A59" s="2"/>
@@ -3147,10 +3376,10 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
       <c r="R59" s="6"/>
-      <c r="S59" s="8"/>
+      <c r="S59" s="6"/>
       <c r="T59" s="8"/>
       <c r="U59" s="6"/>
-      <c r="V59" s="2"/>
+      <c r="V59" s="3"/>
       <c r="W59" s="8"/>
     </row>
     <row r="60" spans="1:23" ht="17.149999999999999" customHeight="1">
@@ -3172,10 +3401,10 @@
       <c r="P60" s="6"/>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
-      <c r="S60" s="8"/>
+      <c r="S60" s="6"/>
       <c r="T60" s="8"/>
       <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
+      <c r="V60" s="8"/>
       <c r="W60" s="6"/>
     </row>
     <row r="61" spans="1:23" ht="17.149999999999999" customHeight="1">
@@ -3183,7 +3412,7 @@
       <c r="B61" s="3"/>
       <c r="C61" s="2"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="4"/>
+      <c r="E61" s="2"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -3197,11 +3426,186 @@
       <c r="P61" s="6"/>
       <c r="Q61" s="6"/>
       <c r="R61" s="6"/>
-      <c r="S61" s="8"/>
-      <c r="T61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="8"/>
       <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
+      <c r="V61" s="2"/>
       <c r="W61" s="6"/>
+    </row>
+    <row r="62" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="6"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="8"/>
+    </row>
+    <row r="63" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="6"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="6"/>
+    </row>
+    <row r="64" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="8"/>
+      <c r="U64" s="6"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="6"/>
+    </row>
+    <row r="65" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
+      <c r="R65" s="6"/>
+      <c r="S65" s="8"/>
+      <c r="T65" s="8"/>
+      <c r="U65" s="6"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="8"/>
+    </row>
+    <row r="66" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="8"/>
+      <c r="T66" s="8"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="8"/>
+    </row>
+    <row r="67" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="8"/>
+      <c r="T67" s="8"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+    </row>
+    <row r="68" spans="1:23" ht="17.149999999999999" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="8"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
+      <c r="V68" s="6"/>
+      <c r="W68" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
